--- a/EtchingData/OriginData.xlsx
+++ b/EtchingData/OriginData.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ningtan/machinelearning/PSMs_ML/EtchingData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ningtan/machinelearning/PSMs_ML_1226/EtchingData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D9661C-0525-EE4C-8F4B-B37B7BFE9EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7B2E7C-40B6-E745-BA9D-BC0F9E6FE989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="2600" windowWidth="21740" windowHeight="12620" xr2:uid="{7E21935B-644F-C443-8C8E-868C9D3D8004}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" xr2:uid="{7E21935B-644F-C443-8C8E-868C9D3D8004}"/>
   </bookViews>
   <sheets>
-    <sheet name="12.16" sheetId="1" r:id="rId1"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'12.16'!$M$1:$M$464</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'12.16'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1'!$M$1:$M$463</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18264" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18227" uniqueCount="793">
   <si>
     <t>Structure</t>
   </si>
@@ -4471,23 +4471,6 @@
     <t>Spiro-TTB</t>
   </si>
   <si>
-    <r>
-      <t>FA0.9Cs0.07MA0.03Pb(I0.975Br0.025</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="4"/>
-        <charset val="1"/>
-      </rPr>
-      <t>)₃</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Py3</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -4807,7 +4790,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="57">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5213,14 +5196,6 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Cambria Math"/>
-      <family val="4"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -5891,7 +5866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40489F9D-86F6-4F40-A7A8-56678A2304BF}">
-  <dimension ref="A1:AX465"/>
+  <dimension ref="A1:AX464"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="36.1640625" customWidth="1"/>
@@ -6016,7 +5991,7 @@
         <v>30</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AG1" s="5" t="s">
         <v>31</v>
@@ -6031,7 +6006,7 @@
         <v>34</v>
       </c>
       <c r="AK1" s="5" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AL1" s="5" t="s">
         <v>35</v>
@@ -6046,7 +6021,7 @@
         <v>38</v>
       </c>
       <c r="AP1" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AQ1" s="5" t="s">
         <v>39</v>
@@ -6061,10 +6036,10 @@
         <v>42</v>
       </c>
       <c r="AU1" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="AV1" s="5" t="s">
         <v>792</v>
-      </c>
-      <c r="AV1" s="5" t="s">
-        <v>793</v>
       </c>
       <c r="AW1" s="5" t="s">
         <v>43</v>
@@ -75479,78 +75454,78 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="460" spans="1:50" ht="21">
+    <row r="460" spans="1:50" ht="34">
       <c r="A460" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B460" t="s">
-        <v>672</v>
+        <v>69</v>
+      </c>
+      <c r="B460" s="9" t="s">
+        <v>779</v>
       </c>
       <c r="C460" t="s">
-        <v>48</v>
-      </c>
-      <c r="D460" s="10" t="s">
-        <v>658</v>
+        <v>273</v>
+      </c>
+      <c r="D460" t="s">
+        <v>48</v>
       </c>
       <c r="E460" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="F460" s="14" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G460" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H460" s="14" t="s">
-        <v>48</v>
+        <v>72</v>
+      </c>
+      <c r="H460" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="I460" s="14" t="s">
-        <v>48</v>
+        <v>780</v>
       </c>
       <c r="J460" s="14" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="K460" s="9" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="L460" s="16" t="s">
-        <v>779</v>
+        <v>511</v>
       </c>
       <c r="M460" s="16">
-        <v>20.05</v>
+        <v>1</v>
       </c>
       <c r="N460" s="14" t="s">
-        <v>358</v>
+        <v>781</v>
       </c>
       <c r="O460" s="14" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="P460" s="14" t="s">
         <v>68</v>
       </c>
       <c r="Q460" s="12" t="s">
-        <v>156</v>
+        <v>782</v>
       </c>
       <c r="R460">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="S460">
-        <v>35</v>
-      </c>
-      <c r="T460" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="U460" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="V460">
-        <v>1064</v>
-      </c>
-      <c r="W460">
-        <v>532</v>
-      </c>
-      <c r="X460">
-        <v>532</v>
+        <v>1</v>
+      </c>
+      <c r="T460">
+        <v>150</v>
+      </c>
+      <c r="U460">
+        <v>10</v>
+      </c>
+      <c r="V460" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="W460" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="X460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="Y460" s="12" t="s">
         <v>48</v>
@@ -75567,8 +75542,8 @@
       <c r="AC460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AD460" t="s">
-        <v>60</v>
+      <c r="AD460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AE460" s="12" t="s">
         <v>48</v>
@@ -75576,8 +75551,8 @@
       <c r="AF460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AG460">
-        <v>50</v>
+      <c r="AG460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AH460" s="12" t="s">
         <v>48</v>
@@ -75585,14 +75560,14 @@
       <c r="AI460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AJ460">
-        <v>30</v>
+      <c r="AJ460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AK460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AL460">
-        <v>100</v>
+      <c r="AL460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AM460" s="12" t="s">
         <v>48</v>
@@ -75600,14 +75575,14 @@
       <c r="AN460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AO460">
-        <v>65</v>
+      <c r="AO460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AP460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AQ460">
-        <v>100</v>
+      <c r="AQ460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AR460" s="12" t="s">
         <v>48</v>
@@ -75615,8 +75590,8 @@
       <c r="AS460" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AT460">
-        <v>50</v>
+      <c r="AT460" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AU460" s="12" t="s">
         <v>48</v>
@@ -75625,10 +75600,10 @@
         <v>48</v>
       </c>
       <c r="AW460" s="12" t="s">
-        <v>404</v>
+        <v>48</v>
       </c>
       <c r="AX460" s="17">
-        <v>22.67</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="461" spans="1:50" ht="34">
@@ -75636,7 +75611,7 @@
         <v>69</v>
       </c>
       <c r="B461" s="9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C461" t="s">
         <v>273</v>
@@ -75657,7 +75632,7 @@
         <v>145</v>
       </c>
       <c r="I461" s="14" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="J461" s="14" t="s">
         <v>99</v>
@@ -75669,10 +75644,10 @@
         <v>511</v>
       </c>
       <c r="M461" s="16">
-        <v>1</v>
+        <v>20.8</v>
       </c>
       <c r="N461" s="14" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O461" s="14" t="s">
         <v>155</v>
@@ -75681,7 +75656,7 @@
         <v>68</v>
       </c>
       <c r="Q461" s="12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="R461">
         <v>90</v>
@@ -75719,8 +75694,8 @@
       <c r="AC461" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AD461" s="12" t="s">
-        <v>48</v>
+      <c r="AD461" t="s">
+        <v>60</v>
       </c>
       <c r="AE461" s="12" t="s">
         <v>48</v>
@@ -75780,18 +75755,18 @@
         <v>48</v>
       </c>
       <c r="AX461" s="17">
-        <v>24.2</v>
+        <v>22.1</v>
       </c>
     </row>
-    <row r="462" spans="1:50" ht="34">
+    <row r="462" spans="1:50" ht="21">
       <c r="A462" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B462" s="9" t="s">
-        <v>780</v>
+      <c r="B462" t="s">
+        <v>211</v>
       </c>
       <c r="C462" t="s">
-        <v>273</v>
+        <v>368</v>
       </c>
       <c r="D462" t="s">
         <v>48</v>
@@ -75805,47 +75780,47 @@
       <c r="G462" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H462" s="10" t="s">
-        <v>145</v>
+      <c r="H462" s="14" t="s">
+        <v>783</v>
       </c>
       <c r="I462" s="14" t="s">
-        <v>781</v>
+        <v>48</v>
       </c>
       <c r="J462" s="14" t="s">
         <v>99</v>
       </c>
       <c r="K462" s="9" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="L462" s="16" t="s">
         <v>511</v>
       </c>
       <c r="M462" s="16">
-        <v>20.8</v>
+        <v>1</v>
       </c>
       <c r="N462" s="14" t="s">
-        <v>782</v>
+        <v>358</v>
       </c>
       <c r="O462" s="14" t="s">
-        <v>155</v>
+        <v>784</v>
       </c>
       <c r="P462" s="14" t="s">
         <v>68</v>
       </c>
       <c r="Q462" s="12" t="s">
-        <v>783</v>
+        <v>223</v>
       </c>
       <c r="R462">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="S462">
-        <v>1</v>
-      </c>
-      <c r="T462">
-        <v>150</v>
-      </c>
-      <c r="U462">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="T462" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="U462" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="V462" s="12" t="s">
         <v>48</v>
@@ -75871,8 +75846,8 @@
       <c r="AC462" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AD462" t="s">
-        <v>60</v>
+      <c r="AD462" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="AE462" s="12" t="s">
         <v>48</v>
@@ -75932,18 +75907,18 @@
         <v>48</v>
       </c>
       <c r="AX462" s="17">
-        <v>22.1</v>
+        <v>24.36</v>
       </c>
     </row>
-    <row r="463" spans="1:50" ht="21">
+    <row r="463" spans="1:50" ht="34">
       <c r="A463" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B463" t="s">
-        <v>211</v>
+      <c r="B463" s="9" t="s">
+        <v>785</v>
       </c>
       <c r="C463" t="s">
-        <v>368</v>
+        <v>48</v>
       </c>
       <c r="D463" t="s">
         <v>48</v>
@@ -75955,10 +75930,10 @@
         <v>71</v>
       </c>
       <c r="G463" s="14" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="H463" s="14" t="s">
-        <v>784</v>
+        <v>699</v>
       </c>
       <c r="I463" s="14" t="s">
         <v>48</v>
@@ -75970,28 +75945,28 @@
         <v>55</v>
       </c>
       <c r="L463" s="16" t="s">
-        <v>511</v>
+        <v>786</v>
       </c>
       <c r="M463" s="16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="N463" s="14" t="s">
-        <v>358</v>
+        <v>141</v>
       </c>
       <c r="O463" s="14" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="P463" s="14" t="s">
         <v>68</v>
       </c>
       <c r="Q463" s="12" t="s">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="R463">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="S463">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="T463" s="12" t="s">
         <v>48</v>
@@ -76084,163 +76059,11 @@
         <v>48</v>
       </c>
       <c r="AX463" s="17">
-        <v>24.36</v>
+        <v>25.81</v>
       </c>
     </row>
-    <row r="464" spans="1:50" ht="34">
-      <c r="A464" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B464" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="C464" t="s">
-        <v>48</v>
-      </c>
-      <c r="D464" t="s">
-        <v>48</v>
-      </c>
-      <c r="E464" t="s">
-        <v>48</v>
-      </c>
-      <c r="F464" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G464" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H464" s="14" t="s">
-        <v>699</v>
-      </c>
-      <c r="I464" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J464" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K464" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L464" s="16" t="s">
-        <v>787</v>
-      </c>
-      <c r="M464" s="16">
-        <v>1.01</v>
-      </c>
-      <c r="N464" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="O464" s="14" t="s">
-        <v>788</v>
-      </c>
-      <c r="P464" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="R464">
-        <v>100</v>
-      </c>
-      <c r="S464">
-        <v>60</v>
-      </c>
-      <c r="T464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="U464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="V464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="W464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="X464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AO464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AS464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AT464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AU464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AW464" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX464" s="17">
-        <v>25.81</v>
-      </c>
-    </row>
-    <row r="465" spans="2:2">
-      <c r="B465" s="9"/>
+    <row r="464" spans="1:50">
+      <c r="B464" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
